--- a/src/attributions/attributions_ig_traj_397.xlsx
+++ b/src/attributions/attributions_ig_traj_397.xlsx
@@ -1568,46 +1568,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.001698264351214024</v>
+        <v>-0.01666298845840682</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09032461491966785</v>
+        <v>0.07039080198723226</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1445922920868696</v>
+        <v>-0.04549141488702976</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003036118857995068</v>
+        <v>0.08211634895411238</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04318682327874841</v>
+        <v>0.01975825299154824</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0583179002477438</v>
+        <v>-0.03154564313627246</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1619,22 +1619,22 @@
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05869909040082785</v>
+        <v>-0.02512323500782544</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01533627059170748</v>
+        <v>0.04166993841483414</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1000685962435049</v>
+        <v>-0.06916655074053936</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
@@ -1646,25 +1646,25 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.05535741593732631</v>
+        <v>0.03525809710678342</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.001637565456182999</v>
+        <v>-0.04043053064459316</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.07044033317750263</v>
+        <v>-0.02144549020919961</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
@@ -1673,76 +1673,76 @@
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.04315363701277057</v>
+        <v>0.01131811618305495</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.01657214440420051</v>
+        <v>-0.06495667477541128</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1660647138955663</v>
+        <v>-0.1146933255603759</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
         <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.09248739708644117</v>
+        <v>-0.09786728573888187</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2882602814315183</v>
+        <v>0.03623324894481225</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1912178635465354</v>
+        <v>-0.2716839543236987</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.959733318195056e-11</v>
+        <v>-4.171421920361549e-11</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.02483185525781575</v>
+        <v>0.006901005569138758</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.01118249647584029</v>
+        <v>0.02371195138946624</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1754,28 +1754,28 @@
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.03202559149904778</v>
+        <v>0.07489615449928465</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.03795674785409718</v>
+        <v>-0.001148348329240803</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.3157971778643808</v>
+        <v>0.04242717743710198</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,19 +1784,19 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.129316729836858</v>
+        <v>-0.1123054716632543</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1886901713151593</v>
+        <v>0.1270651653793568</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.06086694736161714</v>
+        <v>-0.1294795756309746</v>
       </c>
       <c r="BZ3" t="n">
         <v>-0</v>
@@ -1805,52 +1805,52 @@
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.007730105949160554</v>
+        <v>0.06892978740845801</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.01914368669473265</v>
+        <v>-0.02436167583960757</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.09934947987762371</v>
+        <v>0.07078778980529507</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.01594974215373174</v>
+        <v>-0.02935163262409996</v>
       </c>
       <c r="CN3" t="n">
         <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1082209519631139</v>
+        <v>0.0001915758123760395</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.3591433640102047</v>
+        <v>-0.06934354114731077</v>
       </c>
       <c r="CR3" t="n">
         <v>-0</v>
@@ -1859,193 +1859,193 @@
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.0209680995166651</v>
+        <v>0.05760369379510151</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.01335847091884826</v>
+        <v>-0.042212054197959</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.06263505741327885</v>
+        <v>0.02293932743237435</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.01586348001343385</v>
+        <v>0.04840739240098232</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.000729785930812659</v>
+        <v>0.0005546169837249849</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.01052749616062525</v>
+        <v>0.146271811099731</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.005330051715992531</v>
+        <v>0.07837854148580435</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.06009334430105116</v>
+        <v>0.02883875959479583</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2484679722632705</v>
+        <v>-0.09005267891778683</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.03940522347465738</v>
+        <v>0.02831121861453455</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.04025037499413298</v>
+        <v>0.1447147470385168</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.001279168249224212</v>
+        <v>-0.0948930156593905</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.01492594870933297</v>
+        <v>0.03407715942473885</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.08235560091449158</v>
+        <v>0.01297887657157774</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.04124649425036499</v>
+        <v>0.05627471905902899</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.01599068809864547</v>
+        <v>0.01227479725254896</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0407433355744234</v>
+        <v>-0.01205864023058558</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.03909592641895326</v>
+        <v>0.09845407094902488</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.002172451296256502</v>
+        <v>0.05859079972059512</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.02190825290973622</v>
+        <v>-0.04168640819030334</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.04650643720458589</v>
+        <v>0.03774237516974358</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,22 +2054,22 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.09424774017042083</v>
+        <v>0.1927886263595462</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.05131333581879809</v>
+        <v>0.03245808271646998</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.04828418536953422</v>
+        <v>-0.01672280766266094</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
@@ -2081,19 +2081,19 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.0860866583129906</v>
+        <v>0.1343763596465818</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.001114453405841115</v>
+        <v>0.001711419058019002</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.01081141066184009</v>
+        <v>0.006733714729475719</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2102,19 +2102,19 @@
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.06557509196053077</v>
+        <v>0.1396603667094916</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.06167596332497448</v>
+        <v>0.002173097255673581</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
@@ -2123,13 +2123,13 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
@@ -2140,16 +2140,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.149714505735255</v>
+        <v>0.09226981745384534</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.02776798221020815</v>
+        <v>-0.01856625969060247</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03581899336885915</v>
+        <v>-0.01192125925403275</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,25 +2161,25 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06869424425299396</v>
+        <v>0.06096872505343084</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03126137445160049</v>
+        <v>0.02506796669841802</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.02300241779406858</v>
+        <v>-0.008736818884909788</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -2188,76 +2188,76 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1139370858069197</v>
+        <v>0.033285511331149</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03778838007874064</v>
+        <v>-0.02700241233638966</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05847148647745175</v>
+        <v>-0.02036920473164866</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02080578828302994</v>
+        <v>-0.009286464003635862</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.01051684205525188</v>
+        <v>-0.01374345326486251</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.0121702722523295</v>
+        <v>-0.03134184449376615</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.04333676702967609</v>
+        <v>0.07001754799210724</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.04704702279942756</v>
+        <v>-0.028546460509464</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.008722714290258653</v>
+        <v>0.0276755865302764</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,25 +2275,25 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3138036199629953</v>
+        <v>0.171075120017556</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01287677583505899</v>
+        <v>-0.03861200265285931</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1729152799741269</v>
+        <v>-0.06127298125259477</v>
       </c>
       <c r="AY4" t="n">
         <v>-0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0001504463678475821</v>
+        <v>-0.009166767811536173</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.02861827062355512</v>
+        <v>-0.005539611743168439</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.0338608778599664</v>
+        <v>-0.007995709080978672</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.006717785166220515</v>
+        <v>-0.003078910585397003</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.08131727426576313</v>
+        <v>0.01699638065692019</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02068984058419992</v>
+        <v>0.04021126487026511</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,16 +2356,16 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1768426274462216</v>
+        <v>0.1230361438120047</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01926442549769245</v>
+        <v>-0.03875220622357019</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.02542960425855786</v>
+        <v>-0.003394907595631771</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -2374,55 +2374,55 @@
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.05398354762436543</v>
+        <v>-0.05320792565765173</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002983381675328014</v>
+        <v>0.04405061915671392</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.008802435325876965</v>
+        <v>0.0009888741491620359</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.02502165489139454</v>
+        <v>-0.03290123547042136</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.09303728637050346</v>
+        <v>0.06062748486578445</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.129458148168921</v>
+        <v>0.0364112183099576</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2437,49 +2437,49 @@
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.0450767953962698</v>
+        <v>-0.05657068309554283</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.02781550249511222</v>
+        <v>0.0493157979249533</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.00315865149758666</v>
+        <v>0.005708011651810745</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.05350148353150871</v>
+        <v>-0.02209832652228914</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.001704629051339849</v>
+        <v>-0.003130535085469627</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.0003944074967818237</v>
+        <v>0.0009385506421823981</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,25 +2491,25 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.07925054506308804</v>
+        <v>-0.03540042644983372</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.03323155568436922</v>
+        <v>0.01700496921543127</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.01984491122730684</v>
+        <v>-0.03474690425187307</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.04463334667105781</v>
+        <v>0.009032773136389342</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.06209097585508522</v>
+        <v>0.02700171742548056</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01428706706071575</v>
+        <v>-0.003436317481659035</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2539,31 +2539,31 @@
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.02799842412526388</v>
+        <v>-0.03454164101052087</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.06107735198091238</v>
+        <v>0.03300217508031995</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.008762970588577133</v>
+        <v>0.004155998892666203</v>
       </c>
       <c r="EK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,73 +2572,73 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.02177411607888308</v>
+        <v>-0.02876935361347386</v>
       </c>
       <c r="EQ4" t="n">
         <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.02555731143021093</v>
+        <v>-0.03127645007721503</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.005417067809084303</v>
+        <v>0.000787474151756844</v>
       </c>
       <c r="ET4" t="n">
         <v>-0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.0439356461413449</v>
+        <v>-0.06161114169884784</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.01016570761156619</v>
+        <v>0.04556583995383913</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.0190185787256981</v>
+        <v>-0.001019500250383639</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.02249950691385786</v>
+        <v>-0.03663806520268775</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.03893135557581847</v>
+        <v>0.01464831515048575</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01372027517053958</v>
+        <v>0.01298703316118265</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.0006081785806548758</v>
+        <v>0.000504648778495951</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.002871389583045982</v>
+        <v>0.07777018275589208</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0004447571696297291</v>
+        <v>-0.000376366375493825</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,34 +2674,34 @@
         <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.0077399824794758</v>
+        <v>-0.04382457202921951</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.020708200836567</v>
+        <v>0.008982410783324688</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03842279882539255</v>
+        <v>0.1550882031852694</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03772126269214617</v>
+        <v>0.02432901263771919</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02429064866192508</v>
+        <v>-0.06999603025588219</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,34 +2736,34 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009447666336808182</v>
+        <v>0.1279274658462674</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01950336129371932</v>
+        <v>-0.01213519617422661</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.002777682879670186</v>
+        <v>-0.008731014917484986</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.009185044145854747</v>
+        <v>0.06519268443859785</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.02473643255117674</v>
+        <v>-0.06514866804431693</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01886603689789432</v>
+        <v>0.03233336017104861</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
@@ -2790,19 +2790,19 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.008723044933638811</v>
+        <v>-0.02935690570857856</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.006030071692178677</v>
+        <v>-0.06863587098645935</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.004661000740350972</v>
+        <v>-0.0162583125765493</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2811,13 +2811,13 @@
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01105927260255084</v>
+        <v>0.06045650119404039</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,37 +2826,37 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01976971881468227</v>
+        <v>0.03379460719340169</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.004522180198708965</v>
+        <v>-0.06704271606281101</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0508213226349291</v>
+        <v>0.2895180214264814</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.06543108999997677</v>
+        <v>-0.1156045543471239</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.02411536069817988</v>
+        <v>-0.1166930800385507</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2865,28 +2865,28 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01063490209974794</v>
+        <v>-0.002551118586138777</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.006795319203968571</v>
+        <v>-0.01019058322231557</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.003166623107207149</v>
+        <v>-0.01044123915603524</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,37 +2895,37 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03654566923716939</v>
+        <v>0.02559412902894941</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01888008075855696</v>
+        <v>0.07027515997138656</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.005991175227395509</v>
+        <v>0.07435939220600349</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.02106238247269873</v>
+        <v>0.2295717600085448</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,13 +2934,13 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.02925020711901917</v>
+        <v>-0.01219062412379682</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.00232379666633151</v>
+        <v>-0.05510523192903682</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2952,19 +2952,19 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.006493092217834515</v>
+        <v>-0.07929501198092254</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01571979183097041</v>
+        <v>-0.01977954918440418</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01422699216706482</v>
+        <v>0.06427778433703901</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2976,52 +2976,52 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.003564089179364146</v>
+        <v>-0.08992246259826424</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.007355522678756745</v>
+        <v>0.06077326304683454</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.005915552769273313</v>
+        <v>0.04710260621843368</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0007156205260100591</v>
+        <v>-0.07098933838378699</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01548128126426912</v>
+        <v>-0.029687303402661</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.02063238255990376</v>
+        <v>0.06468094133549705</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.01831370171781652</v>
+        <v>-0.02927130702864751</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.02247948663243271</v>
+        <v>-0.04982395223244403</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.002344185166505159</v>
+        <v>0.0007843258843761671</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,31 +3054,31 @@
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01074260525520543</v>
+        <v>-0.04623923788978952</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01726434608075239</v>
+        <v>0.007113034135509664</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.006428855994417108</v>
+        <v>0.001782796647137765</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,7 +3087,7 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.02175322516052989</v>
+        <v>0.03871824191998791</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01605942835475044</v>
+        <v>-0.03950421762777955</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.003624257915941022</v>
+        <v>0.07568785569371329</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
@@ -3114,34 +3114,34 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.001817992615308916</v>
+        <v>0.003723325193808195</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.001017507856137674</v>
+        <v>-0.06483219041432636</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01758117057220966</v>
+        <v>0.02038963042254257</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.009931991343501614</v>
+        <v>-0.01952640391957471</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,43 +3150,43 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.03094515291277698</v>
+        <v>-0.1248975024622279</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.006656237423974093</v>
+        <v>0.0640294071848295</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.004402686883933253</v>
+        <v>-0.07976320282226565</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01579354371600522</v>
+        <v>-0.04141328511547317</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01755493864336319</v>
+        <v>0.04685011969442968</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
@@ -3195,46 +3195,46 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.0231575383780902</v>
+        <v>-0.07393104622625554</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02700032954092544</v>
+        <v>0.02535311004664218</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01718952318767884</v>
+        <v>0.03135326169444861</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.001317623452170691</v>
+        <v>0.0144494044885203</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0001796630271860536</v>
+        <v>-0.0003712807551200009</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02481093501242979</v>
+        <v>-0.06076407179056041</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
@@ -3243,25 +3243,25 @@
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01405848636208366</v>
+        <v>-0.02857098629383688</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC5" t="n">
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.004618092596903043</v>
+        <v>0.03484129823317456</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4559946977108292</v>
+        <v>0.1418523948741275</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1437874557152473</v>
+        <v>-0.05315192691066621</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.05338958432052199</v>
+        <v>-0.01958121573442659</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,25 +3868,25 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2579406960596352</v>
+        <v>0.126021230141038</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03953832070310201</v>
+        <v>-0.02043776364259639</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.08617301584639329</v>
+        <v>-0.03002537036194633</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
@@ -3898,52 +3898,52 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1478179770244236</v>
+        <v>0.03854638862912603</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0368271281346227</v>
+        <v>-0.03329948369428661</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005945037065637771</v>
+        <v>-0.03955184696868615</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05650102897639715</v>
+        <v>-0.01485389990027096</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.02344142287001724</v>
+        <v>-0.02232543858059755</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01472856783133344</v>
+        <v>-0.04280149808537052</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
@@ -3955,25 +3955,25 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.08886699058230781</v>
+        <v>0.09075709681672804</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.06795647690123482</v>
+        <v>-0.03604517698189594</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.06009801107247891</v>
+        <v>0.02837289968276628</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.6432196279590225</v>
+        <v>0.2164330670521514</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.04571051416396374</v>
+        <v>-0.06148910393595624</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2314701247779373</v>
+        <v>-0.08514888798916316</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.03744493830574813</v>
+        <v>-0.02101232620212365</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.03984409919667024</v>
+        <v>-0.01117843110985459</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1039505471847601</v>
+        <v>-0.01595082716196479</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.06618366313147248</v>
+        <v>0.004191051024264258</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1275764180207766</v>
+        <v>0.0118876266338977</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.06778339226952768</v>
+        <v>0.05066001242695392</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,25 +4063,25 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.3322504882083956</v>
+        <v>0.1493220531031381</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.01859597639307958</v>
+        <v>-0.03109255294750523</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.01561269447990988</v>
+        <v>-0.02485908962413657</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,46 +4090,46 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.123547995420889</v>
+        <v>-0.06414220640716861</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.02697185256381011</v>
+        <v>0.05322995456179315</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.03347561043596822</v>
+        <v>0.00591050202952836</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.0295613207580282</v>
+        <v>-0.03717021198554999</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.1613882611403268</v>
+        <v>0.08658483990279733</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1909433039363018</v>
+        <v>0.04157971138140314</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4144,49 +4144,49 @@
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.09761622922973102</v>
+        <v>-0.06418671938090643</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.070083779693545</v>
+        <v>0.05925081371398464</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.02882455030609429</v>
+        <v>0.01162825827659066</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.06252486370759369</v>
+        <v>-0.02887324309089622</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.01261010894958277</v>
+        <v>-0.004371476200488779</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.002111453266131531</v>
+        <v>-0.009136992844780936</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -4198,19 +4198,19 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.09316593238116001</v>
+        <v>-0.03941127031936057</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.05651178795039629</v>
+        <v>0.006082577049087649</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.02641938791152773</v>
+        <v>-0.02715255299491923</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,76 +4225,76 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.04101005616281093</v>
+        <v>0.01179037116461917</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.0528546529883677</v>
+        <v>0.0308613442171229</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.04771887448834205</v>
+        <v>0.002226758944365855</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.05129519349923534</v>
+        <v>-0.04162704825810472</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.067758280530078</v>
+        <v>0.0560994583876519</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.00174035448372136</v>
+        <v>0.002291887908973427</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.09337790186941065</v>
+        <v>-0.03352783175190411</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.06043854487165377</v>
+        <v>-0.0323874479960485</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.06286620303337137</v>
+        <v>-0.002652543808300011</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,43 +4306,43 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.108091733494472</v>
+        <v>-0.07104538884852628</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.04282519876570012</v>
+        <v>0.05606300332750595</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.04179836489300566</v>
+        <v>-6.055385855869513e-05</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.005265651684507567</v>
+        <v>-0.04306487894539397</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.06020137748472168</v>
+        <v>0.02747968143217077</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.002064218066986844</v>
+        <v>0.01887447679712188</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
@@ -4354,25 +4354,25 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.005354642135566605</v>
+        <v>-0.006842616575315841</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.06053950023645613</v>
+        <v>0.08642514509703257</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.03625059855967578</v>
+        <v>-0.01648126128253708</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4384,31 +4384,31 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03887839450413223</v>
+        <v>-0.05503135887480655</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.04213652380020357</v>
+        <v>0.0219226037023735</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4985,25 +4985,25 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.07800226553318974</v>
+        <v>0.1782921261821422</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.01499663365721613</v>
+        <v>0.009946676687526785</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02599479101141196</v>
+        <v>-0.06937351374085841</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02403564869042484</v>
+        <v>0.2126994806142326</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,79 +5021,79 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02063751418909289</v>
+        <v>-0.02802695863963081</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.000769072079744465</v>
+        <v>-0.001380195966942591</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.003233816149634494</v>
+        <v>0.06625223708800759</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01318986620280625</v>
+        <v>-0.03475892647684548</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02002827139485606</v>
+        <v>0.03729319679264537</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01489391499927191</v>
+        <v>-0.01507663982369245</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01483792305531875</v>
+        <v>-0.06099161665026547</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.003106388305953578</v>
+        <v>0.004437470510114313</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01370542956894517</v>
+        <v>0.08779136473619317</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,37 +5102,37 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.01633103969284404</v>
+        <v>-0.004451294323477806</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.01490371052510201</v>
+        <v>-0.07249440304981929</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1001304419689981</v>
+        <v>0.287679772690542</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.0116116350792308</v>
+        <v>-0.1234852436533008</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.02095227882211252</v>
+        <v>-0.1138857649716193</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5141,40 +5141,40 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01488069347131692</v>
+        <v>-0.02065677294586579</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.01532019550585599</v>
+        <v>-0.03836607224800281</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.004539876365938006</v>
+        <v>-0.01465201904063175</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.04315715782166764</v>
+        <v>0.01550108197001369</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,16 +5183,16 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.03052435758205739</v>
+        <v>0.06975288683272932</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01078782999296582</v>
+        <v>0.05005268776791643</v>
       </c>
       <c r="BR9" t="n">
         <v>-0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -5201,25 +5201,25 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.03636300969793031</v>
+        <v>0.1876220633658348</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.02356810172248408</v>
+        <v>-0.01572465442800384</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.02068146297118289</v>
+        <v>-0.03204996701403009</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.009099937642156844</v>
+        <v>-0.06729434405496618</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0004306210347867127</v>
+        <v>0.005032325120420663</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01512210745385511</v>
+        <v>0.04292523246673988</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5255,103 +5255,103 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.01246443838942189</v>
+        <v>-0.04124777683638367</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.01443099888127456</v>
+        <v>0.1412452095270334</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.03373785853223209</v>
+        <v>0.01225983735583234</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.002558835629002163</v>
+        <v>-0.06069285945868534</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0006894424565565757</v>
+        <v>0.003535506655759142</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.01767774585614089</v>
+        <v>0.05207110818674794</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.01224158471410043</v>
+        <v>-0.0264480083836536</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03198693222189947</v>
+        <v>-0.04399907385261848</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01488646096661662</v>
+        <v>0.08745273163296707</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.005021260054592616</v>
+        <v>-0.04633099820586165</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.02051524090170383</v>
+        <v>-0.03098454314257757</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.0008155618424003642</v>
+        <v>0.01636322644471736</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,25 +5363,25 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.02902204871236597</v>
+        <v>0.01708787217880463</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.0401793314938265</v>
+        <v>-0.08013755817887111</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.008149148483797063</v>
+        <v>0.02469829828926631</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,76 +5390,76 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.005002908558258628</v>
+        <v>0.01613906808713152</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0003004651003700006</v>
+        <v>-0.03066507685645715</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.001779378110469817</v>
+        <v>-0.01307042922848741</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.002020863315854582</v>
+        <v>-0.02243046630268423</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.02056692485602247</v>
+        <v>-0.1153367162924789</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.0490404383123416</v>
+        <v>-0.113529057345617</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.003231390990977015</v>
+        <v>-0.07073003834289157</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.001844932283075199</v>
+        <v>-0.00903438902958446</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.01947323996866248</v>
+        <v>0.03514408142860045</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5471,64 +5471,64 @@
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02212477899358138</v>
+        <v>-0.07052766004584202</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.04198328712623728</v>
+        <v>0.0649519087859159</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.000811969575263077</v>
+        <v>0.03346155381100673</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.004600581392403534</v>
+        <v>0.01473745065157115</v>
       </c>
       <c r="FR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.009963703190071851</v>
+        <v>-0.01893584488648665</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.03741934682712134</v>
+        <v>-0.09808109650932062</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02318459598526812</v>
+        <v>-0.0126109176785597</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
@@ -5537,13 +5537,13 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.006063735650359174</v>
+        <v>-0.009533806518631401</v>
       </c>
       <c r="GE9" t="n">
         <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2478270667923743</v>
+        <v>0.2299720844070678</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08512506288414574</v>
+        <v>-0.06765948333546631</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0770781979050775</v>
+        <v>-0.02848522876977917</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5575,25 +5575,25 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1722098313094498</v>
+        <v>0.2132566463966336</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.04797065910449437</v>
+        <v>-0.05670820721286659</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1045690184382968</v>
+        <v>-0.05769313950502793</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -5602,85 +5602,85 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.07097895114370237</v>
+        <v>0.06733390640322326</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.02380748467264028</v>
+        <v>-0.03726395118716769</v>
       </c>
       <c r="W10" t="n">
-        <v>0.04469909081548586</v>
+        <v>-0.04251035565115332</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.03758959895396671</v>
+        <v>-0.03238519800437596</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.02494016969401811</v>
+        <v>-0.0311256360413102</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.000695699113788891</v>
+        <v>-0.06289030395909354</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02796839100281675</v>
+        <v>0.1129676490712352</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.04162223882050319</v>
+        <v>-0.04868863056407407</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.06333368512197281</v>
+        <v>0.04015151615875519</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.348530941473327</v>
+        <v>0.2716485632005359</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.02562039017347631</v>
+        <v>-0.0859610131759275</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1474885666878201</v>
+        <v>-0.140991945772297</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01421865849824503</v>
+        <v>-0.03479778320800102</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.02693460836792124</v>
+        <v>0.009504425798381023</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.09875804124045706</v>
+        <v>-0.0304795802733523</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.07573239486406186</v>
+        <v>0.006437859464531072</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.06878437784440068</v>
+        <v>0.01504231919469481</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1015049696590581</v>
+        <v>0.04203651301776884</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,49 +5770,49 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1684770396469441</v>
+        <v>0.2241647948238083</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.003130987287477527</v>
+        <v>-0.09756575416348497</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.03524378775302796</v>
+        <v>-0.04675519845189088</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.06159400497161319</v>
+        <v>-0.08947357549938359</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.00838200591831716</v>
+        <v>0.07773832320266458</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.006066550540927041</v>
+        <v>0.005977918496636835</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
@@ -5821,25 +5821,25 @@
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.05178428257874237</v>
+        <v>-0.06105844877336036</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.08129763283459271</v>
+        <v>0.1190489678668816</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.1081007621738944</v>
+        <v>0.07827425663859379</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
@@ -5851,49 +5851,49 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.0403772994016634</v>
+        <v>-0.08340200548075398</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.02993713267277865</v>
+        <v>0.08697387040006364</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.009186629523722822</v>
+        <v>0.01129803524794428</v>
       </c>
       <c r="DA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.0001953386867861715</v>
+        <v>-0.0942604120783803</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.00733212105636209</v>
+        <v>0.06719184021858174</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.02956148125712146</v>
+        <v>-0.04098916005107777</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5905,76 +5905,76 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.05957810821352074</v>
+        <v>-0.02423888735342874</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.05567210868333962</v>
+        <v>0.01732390385351395</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01382138539986824</v>
+        <v>-0.01655407359109254</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.03969055688672352</v>
+        <v>0.05600395957672197</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.03560198865763204</v>
+        <v>0.01459190732880089</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.01003350743242986</v>
+        <v>-0.04751262056720554</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02989436124649403</v>
+        <v>-0.04567495215723456</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0794469477804569</v>
+        <v>0.07798458804563642</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0475510095339919</v>
+        <v>0.005354965819159626</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
@@ -5983,103 +5983,103 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.05981017005087289</v>
+        <v>-0.04974399832788749</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.05187922915136967</v>
+        <v>-0.0651525473312637</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.00910060409603229</v>
+        <v>-0.03829264821112678</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.05193320827638647</v>
+        <v>-0.09483027404689323</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01911574239258216</v>
+        <v>0.08808260425274182</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01262812018257569</v>
+        <v>-0.002882465548311763</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.05321880830924241</v>
+        <v>-0.04504254543581811</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0531198797670234</v>
+        <v>0.07392065763214588</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.0160596240589603</v>
+        <v>-0.01775503813161118</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.004765586636804908</v>
+        <v>0.0105951543490513</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.002377691779092758</v>
+        <v>0.06215256178845437</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.03618285945293647</v>
+        <v>-0.01340676423525005</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
@@ -6091,31 +6091,31 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01010093629088331</v>
+        <v>-0.07719903142145831</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.02850300505104619</v>
+        <v>0.02976431808756982</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6689,46 +6689,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2395905988824716</v>
+        <v>0.07435960875787129</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.02260548145099555</v>
+        <v>-0.02042135398219381</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04473562206476055</v>
+        <v>-0.03445806671491682</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1205635680562197</v>
+        <v>0.0885288333006255</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01222221666999077</v>
+        <v>-0.01292895624565531</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05493009660544945</v>
+        <v>-0.04529414382538708</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6740,25 +6740,25 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05295167435150055</v>
+        <v>0.02157131098365041</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01311600285939977</v>
+        <v>-0.01262121641989418</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03661349611912841</v>
+        <v>-0.003704997656461798</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6773,43 +6773,43 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.038412524725936</v>
+        <v>-0.009703244540491674</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.003095204526185968</v>
+        <v>-0.01648902014107479</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.001194306501342102</v>
+        <v>-0.0273796766160276</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.01416845430461252</v>
+        <v>0.04598643939291438</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.01735261886667699</v>
+        <v>-0.005313062381097782</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.04827334063388542</v>
+        <v>0.0358930387879034</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,34 +6818,34 @@
         <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.285374850279723</v>
+        <v>0.1118474460057605</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.03560797298708263</v>
+        <v>-0.01097720826385508</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.06419068831876769</v>
+        <v>-0.05603791458858498</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,25 +6854,25 @@
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02337494184067121</v>
+        <v>-0.03078862087714548</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.03987018364106877</v>
+        <v>-0.0007546972931511914</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.04741834079586165</v>
+        <v>-0.01295804710227973</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,16 +6881,16 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1129510625623535</v>
+        <v>0.02482149630684948</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.02480448311757739</v>
+        <v>0.0189237468778237</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.09015059929041105</v>
+        <v>0.03929113723291511</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
@@ -6905,28 +6905,28 @@
         <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.149480802393483</v>
+        <v>0.09270499953398512</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.03211092624403375</v>
+        <v>-0.03749112548860806</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.01863947577095644</v>
+        <v>-0.0124648150842703</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.04902187591825779</v>
+        <v>-0.02393924142251188</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.006109415361769141</v>
+        <v>0.02646489691797059</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.004849358026871082</v>
+        <v>0.01909933391104025</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6962,43 +6962,43 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.0572930055195547</v>
+        <v>-0.03893892625743674</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.04343901823266585</v>
+        <v>0.02082067763257045</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06445135950647994</v>
+        <v>0.03149977977751962</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.03245441320855889</v>
+        <v>-0.02531137231734922</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.006617944262692086</v>
+        <v>0.03276528233555822</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.0005349525971945355</v>
+        <v>0.01724298582526754</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7016,22 +7016,22 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.009846164269758867</v>
+        <v>0.001182868449368656</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.04661186430567374</v>
+        <v>0.007383344187481147</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.006311446466177676</v>
+        <v>-0.001764674581481882</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7040,49 +7040,49 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.0540677150857812</v>
+        <v>-0.02258234968821873</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.001799014123649171</v>
+        <v>-0.01862516537813514</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.0100031105582406</v>
+        <v>-0.01604894910791196</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.003012200518026189</v>
+        <v>0.037260191731135</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.007477676727924408</v>
+        <v>0.01570265417298664</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.02234698900503848</v>
+        <v>-0.05002751700142494</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
@@ -7091,31 +7091,31 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02609347614957539</v>
+        <v>0.009208939135583379</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.00127390261319926</v>
+        <v>0.0153671487277361</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.04532877322496617</v>
+        <v>0.03658526369774438</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,22 +7124,22 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.02974494554189926</v>
+        <v>-0.01456103334882168</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.01299851295108574</v>
+        <v>0.03043531170452981</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.009604620613456896</v>
+        <v>-0.002958982148596617</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>-0</v>
@@ -7148,19 +7148,19 @@
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.03069047862797595</v>
+        <v>-0.02756086212068828</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0001019647409090032</v>
+        <v>0.03398919634872191</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01189444131379129</v>
+        <v>0.0134941621585976</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,25 +7169,25 @@
         <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01448912159608468</v>
+        <v>0.006319787705015073</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.00865841660879195</v>
+        <v>0.006618154475441572</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.01738140870856777</v>
+        <v>-0.02166100891261159</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,34 +7196,34 @@
         <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.04301015810713952</v>
+        <v>0.01420365778495408</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.02559257085527348</v>
+        <v>0.0280476085627642</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.004712456038873086</v>
+        <v>-0.04462663512632378</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
@@ -7232,19 +7232,19 @@
         <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.004091093987375454</v>
+        <v>0.003884709073286379</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.02306904632550895</v>
+        <v>-0.002152396749370208</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,60 +7253,60 @@
         <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2380803427978928</v>
+        <v>0.06460761730474206</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.001095746820180034</v>
+        <v>-0.03976783769994867</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1450025907573197</v>
+        <v>-0.04145645498700209</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1743811196094802</v>
+        <v>0.1424726033564387</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01115106823617612</v>
+        <v>-0.06738335948509236</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1132180230339874</v>
+        <v>-0.04564149512120565</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,46 +7315,46 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01588772138096599</v>
+        <v>0.04467062353974834</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01820940800428576</v>
+        <v>-0.02813789053249108</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01241013159543829</v>
+        <v>-0.003807340172570823</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02374188396086672</v>
+        <v>-0.01622659243311611</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01196994959750774</v>
+        <v>-0.0499640030156325</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.004925490112620794</v>
+        <v>0.005090873033467157</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,67 +7363,67 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01675476791111415</v>
+        <v>0.01652759844307718</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.02376916693079306</v>
+        <v>0.002194225202155779</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.05585425681560269</v>
+        <v>-0.01572883437024729</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1853529615329354</v>
+        <v>0.1637162623485005</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.02027829032981919</v>
+        <v>-0.09912406399255302</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.09594175787759122</v>
+        <v>-0.07332605069208521</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.07394063297761189</v>
+        <v>-0.036177434864981</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.02361206256655182</v>
+        <v>-0.03245062156988164</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.04219388597326065</v>
+        <v>0.003038033148571225</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.06996361920194112</v>
+        <v>0.05592997516487121</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -7459,37 +7459,37 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0411344827109453</v>
+        <v>0.05155294529821786</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.005803542065194317</v>
+        <v>0.002336511425675595</v>
       </c>
       <c r="BR13" t="n">
         <v>-0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.08968470917302152</v>
+        <v>0.1276265556986212</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.02260733997654604</v>
+        <v>-0.0312104581411162</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.0273533523770306</v>
+        <v>-0.02139914764391531</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,25 +7498,25 @@
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.0491033465668501</v>
+        <v>-0.02484634854872511</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.00783743761778583</v>
+        <v>0.04037917540697691</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.03547152616640408</v>
+        <v>0.02370872415594644</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0</v>
@@ -7525,40 +7525,40 @@
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.03208795672521764</v>
+        <v>-0.08899972108656749</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0295951683070237</v>
+        <v>0.1099552765867236</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.03450178133857681</v>
+        <v>0.02382908408680162</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.03398590178238301</v>
+        <v>-0.01999269790949697</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
@@ -7567,67 +7567,67 @@
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.007368391805263044</v>
+        <v>0.03353812150893552</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.03254821188564748</v>
+        <v>0.02414459534894652</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.009920023866317525</v>
+        <v>0.01090269593903999</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.00163339553041885</v>
+        <v>-0.01134739034694249</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.005261083148832728</v>
+        <v>0.001208560279236216</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.03031462201352895</v>
+        <v>-0.05516058802472416</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.007757981170398427</v>
+        <v>0.03245378506358727</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.009476880008304933</v>
+        <v>-0.005439929820779572</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
@@ -7639,7 +7639,7 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0008233324902340991</v>
+        <v>0.0111725958985402</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
@@ -7648,10 +7648,10 @@
         <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.02443437726712577</v>
+        <v>-0.04075502702607127</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.0004279496745904572</v>
+        <v>-0.02806834378383859</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
@@ -7660,13 +7660,13 @@
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02534300610358594</v>
+        <v>0.0353333971235213</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,16 +7675,16 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01624500094036718</v>
+        <v>0.01288471780738404</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.02214252609574052</v>
+        <v>0.01659215404847575</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
         <v>-0</v>
@@ -7693,34 +7693,34 @@
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.02866554314194759</v>
+        <v>0.005675959724159987</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.01639738409380994</v>
+        <v>-0.01910058079577379</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.05136565498888223</v>
+        <v>0.01929867894064604</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.0373743266400248</v>
+        <v>-0.02700731137796509</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,40 +7729,40 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0004981469730564256</v>
+        <v>0.0310961410319728</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.03762654463535887</v>
+        <v>0.02115062020011407</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.006352481097524926</v>
+        <v>-0.02297212123507027</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.02274936537047492</v>
+        <v>0.02332765769483513</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02641223831434603</v>
+        <v>0.005482244626128506</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
         <v>0</v>
@@ -7771,37 +7771,37 @@
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01122804921880683</v>
+        <v>-0.002233823549812028</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.02845589955503868</v>
+        <v>-0.06086922627658969</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.001971890349372318</v>
+        <v>0.001905601626657193</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
         <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02210098601869107</v>
+        <v>-0.0005780419422675311</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.03266511051430239</v>
+        <v>0.004816378568321072</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7833,94 +7833,94 @@
         <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1779658055421642</v>
+        <v>-0.1534352162366521</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3043416089955812</v>
+        <v>0.08257882184412951</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.06540997481381394</v>
+        <v>-0.06065796963135665</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1044533697199827</v>
+        <v>-0.0875262265298075</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3141743273965617</v>
+        <v>0.07100715998008233</v>
       </c>
       <c r="N14" t="n">
-        <v>0.04837984246196645</v>
+        <v>-0.01897919444823205</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.03292509387171252</v>
+        <v>-0.02832671343605417</v>
       </c>
       <c r="V14" t="n">
-        <v>0.07007927897998519</v>
+        <v>0.09036094250801825</v>
       </c>
       <c r="W14" t="n">
-        <v>0.005998666685757456</v>
+        <v>0.02612025438424978</v>
       </c>
       <c r="X14" t="n">
         <v>-0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.007001377456999233</v>
+        <v>-0.01937818773157335</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.03651820288423874</v>
+        <v>-0.09131051993881428</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.02691667935205952</v>
+        <v>-0.06462445014791481</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
@@ -7935,46 +7935,46 @@
         <v>-0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.002253872104288313</v>
+        <v>-0.06945026093272766</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.03780276843722351</v>
+        <v>0.06971205949575993</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.05038461061440211</v>
+        <v>0.01295232422510264</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.1217647488737073</v>
+        <v>-0.1176037305229012</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.2073974694958791</v>
+        <v>0.2009698033191528</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.1640918840718496</v>
+        <v>-0.1168495544969728</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
         <v>-0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
@@ -7995,13 +7995,13 @@
         <v>-0</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.02120035932643963</v>
+        <v>-0.01244796828279497</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.04612775026716067</v>
+        <v>-0.1688005357152557</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.04248437365756278</v>
+        <v>-0.08412689612278045</v>
       </c>
       <c r="BH14" t="n">
         <v>-0</v>
@@ -8010,25 +8010,25 @@
         <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.03803117903454503</v>
+        <v>0.04203413986939871</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0.01636859424534997</v>
+        <v>0.04737382906751585</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.1409039784830825</v>
+        <v>0.1220843646444828</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -8037,91 +8037,91 @@
         <v>-0</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0.09628625480457949</v>
+        <v>-0.1018480275574792</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.1247787745919107</v>
+        <v>0.2357787036621045</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.1132924608713821</v>
+        <v>-0.01300236239751214</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.05504809367520185</v>
+        <v>0.06900436654423775</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.06273467160960852</v>
+        <v>-0.001281067542455212</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01656365905743256</v>
+        <v>0.01598431599735241</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.02061206783606422</v>
+        <v>0.02559459727458128</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.03455177348860076</v>
+        <v>0.03490036180191183</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.1001263124559978</v>
+        <v>0.1226600640141564</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV14" t="n">
         <v>-0</v>
@@ -8130,43 +8130,43 @@
         <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.03771000952891824</v>
+        <v>0.05520344351832031</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.05370277550890187</v>
+        <v>-0.004282334755454983</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.02398992093237077</v>
+        <v>0.02391975856864231</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.00315479341646775</v>
+        <v>0.03059388670272564</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.04879069569492268</v>
+        <v>-0.04444725990198312</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.002029219878160479</v>
+        <v>-0.0102540627970658</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8175,22 +8175,22 @@
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.04061717300431603</v>
+        <v>0.003145277290564959</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.02442313967035403</v>
+        <v>-0.03658488683594618</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.04262351006982984</v>
+        <v>0.07463252674168314</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
@@ -8199,58 +8199,58 @@
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>-0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY14" t="n">
-        <v>-0.001663973139575416</v>
+        <v>-0.01934194167769163</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.03289704743536009</v>
+        <v>-0.009181854119283272</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.02786299346047845</v>
+        <v>-0.105023075524064</v>
       </c>
       <c r="EB14" t="n">
         <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.06120066635339683</v>
+        <v>0.02141766591084984</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.09125826652996437</v>
+        <v>0.07280264217353011</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.02668036815934256</v>
+        <v>-0.02502150235355087</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8262,76 +8262,76 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0293554551836835</v>
+        <v>0.02031505972161845</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.03495992820643429</v>
+        <v>-0.04169124196128741</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.02768205745827738</v>
+        <v>-0.01633527376400759</v>
       </c>
       <c r="ET14" t="n">
         <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
         <v>-0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
         <v>0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.04657092535378215</v>
+        <v>0.06125300803343273</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.05832051798786714</v>
+        <v>-0.02673206903383479</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.02734024532360172</v>
+        <v>0.01698106365389879</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.01596287404325158</v>
+        <v>0.09705882430299302</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.04109055325834993</v>
+        <v>-0.04749052764163814</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.04346372814207073</v>
+        <v>-0.1109622523592712</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
         <v>-0</v>
@@ -8340,19 +8340,19 @@
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.01038519542899066</v>
+        <v>0.001480676068626628</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.003744241552520627</v>
+        <v>0.009766557502727974</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.05468135975605013</v>
+        <v>0.04843241530743384</v>
       </c>
       <c r="FU14" t="n">
         <v>0</v>
@@ -8361,37 +8361,37 @@
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.03507453666508758</v>
+        <v>0.03381701801501306</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.04798270810849641</v>
+        <v>-0.05863740273307534</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -8965,25 +8965,25 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3581279038583455</v>
+        <v>0.2684046496261785</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3552174356998367</v>
+        <v>-0.08999330162927725</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1130050512036871</v>
+        <v>-0.1439389990751627</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
@@ -8995,7 +8995,7 @@
         <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2537046594813843</v>
+        <v>0.4427494444868313</v>
       </c>
       <c r="L16" t="n">
         <v>-0</v>
@@ -9004,13 +9004,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3254358246012867</v>
+        <v>-0.1820666280525241</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1267298653896499</v>
+        <v>-0.155884591757202</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -9019,10 +9019,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08130389609941696</v>
+        <v>0.06164538965579346</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
@@ -9031,25 +9031,25 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.03839207642913476</v>
+        <v>-0.1135711162881234</v>
       </c>
       <c r="X16" t="n">
-        <v>0.06926843395899895</v>
+        <v>-0.02136817583636661</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.06229740106313886</v>
+        <v>-0.03429423550676618</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
@@ -9058,10 +9058,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.01749117597296074</v>
+        <v>-0.1427514206053823</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0196229696245853</v>
+        <v>0.0192186471632447</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
@@ -9073,130 +9073,130 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.09841938817287907</v>
+        <v>0.002120015982308101</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.03517844880671162</v>
+        <v>-0.1176246187047301</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.04309221491025407</v>
+        <v>-0.03138408239663648</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
         <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.3445918013999379</v>
+        <v>0.4801605582117728</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.1521829549091281</v>
+        <v>-0.1601760919875667</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.07592623119500976</v>
+        <v>-0.1590543129273896</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.06657721025776749</v>
+        <v>-0.07882769464581399</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.2079256918726379</v>
+        <v>-0.08217974984666125</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.03891899373700823</v>
+        <v>0.03312859475270764</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.154122106477126</v>
+        <v>0.1763206975292707</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.05669989318162814</v>
+        <v>0.1366503158539777</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.08045933601009825</v>
+        <v>0.04668965318061215</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.2099856072932412</v>
+        <v>0.252851987896868</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.07881594609706921</v>
+        <v>-0.08652700440513472</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.03513436995713929</v>
+        <v>-0.04780406231222518</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9208,22 +9208,22 @@
         <v>-0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.05232347192583432</v>
+        <v>-0.0857146562821974</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0526957416533528</v>
+        <v>0.07342276049950039</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.0405568340591172</v>
+        <v>0.04970649361001055</v>
       </c>
       <c r="CJ16" t="n">
         <v>-0</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.05992074009885125</v>
+        <v>-0.219560803912787</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,43 +9247,43 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.01166584046404658</v>
+        <v>0.157766597345025</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.009451687034229645</v>
+        <v>-0.00443090642509688</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
         <v>0</v>
       </c>
       <c r="CV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.0285324634172384</v>
+        <v>-0.07395731214025072</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.04743827807174113</v>
+        <v>0.03216611598367679</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.05604577323704993</v>
+        <v>0.05845344721835259</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD16" t="n">
         <v>0</v>
@@ -9292,19 +9292,19 @@
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.04744950552389281</v>
+        <v>-0.04282801602788711</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.02547523005333088</v>
+        <v>-0.06408912567995943</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.01791648910207516</v>
+        <v>-0.01459213367260927</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
@@ -9313,28 +9313,28 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.03855497942595164</v>
+        <v>-0.04053258954343257</v>
       </c>
       <c r="DP16" t="n">
         <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.0375544353794387</v>
+        <v>0.03933980390089461</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.1048806296580295</v>
+        <v>-0.05582445668890258</v>
       </c>
       <c r="DT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU16" t="n">
         <v>-0</v>
@@ -9343,25 +9343,25 @@
         <v>-0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.01331113302600846</v>
+        <v>0.0815561677915957</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.06298903628448407</v>
+        <v>-0.07335905316987935</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0.06020687650575474</v>
+        <v>0.01000632689682869</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
         <v>0</v>
@@ -9370,22 +9370,22 @@
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.02856862807114661</v>
+        <v>-0.01171698121053032</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.04754001492453719</v>
+        <v>-0.02710982739664446</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.01926735800283681</v>
+        <v>0.06528423862674489</v>
       </c>
       <c r="EL16" t="n">
         <v>-0</v>
@@ -9394,28 +9394,28 @@
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.05101932006740813</v>
+        <v>0.01374945142460317</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.02057828172278819</v>
+        <v>-0.05127894600999567</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.07679226084481514</v>
+        <v>0.0329536770967804</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
@@ -9424,25 +9424,25 @@
         <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.01894552024732665</v>
+        <v>-0.09290896390034599</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.04218501308893562</v>
+        <v>0.04175651180024439</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.05745752044798327</v>
+        <v>0.04769346222915663</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
@@ -9451,10 +9451,10 @@
         <v>-0</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.06900340801714906</v>
+        <v>-0.03901554351208979</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
@@ -9463,16 +9463,16 @@
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.04487161840218304</v>
+        <v>0.07229698684243312</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.02829868126455205</v>
+        <v>-0.002140780904939476</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,7 +9481,7 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.007026706047410248</v>
+        <v>0.0004744290401801745</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,43 +9490,43 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.007608394816626237</v>
+        <v>-0.01271954741693365</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.006727600140629851</v>
+        <v>0.04325107973987475</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
         <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.04633379327015862</v>
+        <v>-0.08014971022000682</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.06260002050707217</v>
+        <v>0.03528877333688642</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
         <v>0</v>
@@ -9537,19 +9537,19 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5392210748165891</v>
+        <v>0.4623466089038754</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2313949923908778</v>
+        <v>-0.4069260743450481</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1917456059448631</v>
+        <v>-0.03065208307854077</v>
       </c>
       <c r="F17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
@@ -9561,19 +9561,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.435116527475411</v>
+        <v>0.4547542429714369</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2436527913080966</v>
+        <v>-0.4783588726174474</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2391524766437628</v>
+        <v>-0.07141344755799986</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9582,88 +9582,88 @@
         <v>-0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1361108834667332</v>
+        <v>0.1477653384222862</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.01419758014113132</v>
+        <v>-0.07656166044260543</v>
       </c>
       <c r="W17" t="n">
-        <v>0.08046189944221187</v>
+        <v>-0.1445286755744148</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1343660002745654</v>
+        <v>-0.1301845790123618</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.007122570402484944</v>
+        <v>-0.1499889178092502</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.02311702069241071</v>
+        <v>-0.1353212523217603</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.06145335053810863</v>
+        <v>0.1595915783719727</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.03187712638626456</v>
+        <v>-0.1179197304224681</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.06743666200884105</v>
+        <v>0.02592268574473216</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
@@ -9672,43 +9672,43 @@
         <v>-0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.4377243569944291</v>
+        <v>0.4313275158577889</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0.007231170670585622</v>
+        <v>-0.1534407081412069</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.04485888336303958</v>
+        <v>-0.2471600598082663</v>
       </c>
       <c r="AY17" t="n">
         <v>-0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>-0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.05358642283509237</v>
+        <v>-0.01772594589156391</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.1103567771034349</v>
+        <v>-0.1040663796259914</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.2404590485592885</v>
+        <v>-0.02479513506138168</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
@@ -9717,7 +9717,7 @@
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,22 +9726,22 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.1082778035228328</v>
+        <v>-0.001127771726936855</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.04795565221303457</v>
+        <v>0.02941143275898878</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.09954952680525518</v>
+        <v>0.113670061182241</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
@@ -9753,43 +9753,43 @@
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.2445477435313177</v>
+        <v>0.3307051626126732</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0.01926335501946112</v>
+        <v>-0.2238553382542826</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0652981316561505</v>
+        <v>-0.1047521664338456</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.0976233934261468</v>
+        <v>-0.1070213428411925</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.02223602754354025</v>
+        <v>0.1834964867180009</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.005055566121770269</v>
+        <v>0.04111809469862753</v>
       </c>
       <c r="CI17" t="n">
         <v>0</v>
@@ -9807,19 +9807,19 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.08081016120433437</v>
+        <v>-0.1712101465703318</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.06582091984189786</v>
+        <v>0.3423491639813416</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.08473953587183645</v>
+        <v>0.1933700640859201</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9831,25 +9831,25 @@
         <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.07211568451681409</v>
+        <v>-0.08988558006118898</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.03739862401397212</v>
+        <v>0.1954565929727177</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.003170369636197583</v>
+        <v>0.03933699403986058</v>
       </c>
       <c r="DA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
@@ -9861,22 +9861,22 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.0525867127268622</v>
+        <v>-0.1293142314070389</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.02417154615878704</v>
+        <v>0.03499654852011827</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.01223560442883044</v>
+        <v>-0.0558905470553803</v>
       </c>
       <c r="DJ17" t="n">
         <v>0</v>
       </c>
       <c r="DK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL17" t="n">
         <v>0</v>
@@ -9888,16 +9888,16 @@
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.04767408732139035</v>
+        <v>-0.06104530186052587</v>
       </c>
       <c r="DP17" t="n">
         <v>0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0.03153003202461213</v>
+        <v>0.07885397506857222</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.07640657248283034</v>
+        <v>-0.005497677297172624</v>
       </c>
       <c r="DS17" t="n">
         <v>-0</v>
@@ -9912,25 +9912,25 @@
         <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.06063056589632058</v>
+        <v>0.0437328051550352</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.009447059043503118</v>
+        <v>-0.05075742618524504</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.04557425563513693</v>
+        <v>-0.06503544593576946</v>
       </c>
       <c r="EB17" t="n">
         <v>0</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
@@ -9942,25 +9942,25 @@
         <v>0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.05920001115115349</v>
+        <v>-0.08473296002425196</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.05682121320582734</v>
+        <v>0.1457229618978676</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.07541652345299499</v>
+        <v>0.0727800646139368</v>
       </c>
       <c r="EK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
         <v>-0</v>
@@ -9969,22 +9969,22 @@
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.0796851322123891</v>
+        <v>-0.02266557224385393</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.02301218617906965</v>
+        <v>0.1255495488986581</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.06903849702111255</v>
+        <v>-0.07651413510248509</v>
       </c>
       <c r="ET17" t="n">
         <v>-0</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
@@ -9993,25 +9993,25 @@
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.08143104726853335</v>
+        <v>-0.1215912643606349</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.04415329239876076</v>
+        <v>0.2031006212012488</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.0169887076356888</v>
+        <v>0.02744230667677093</v>
       </c>
       <c r="FC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
@@ -10023,46 +10023,46 @@
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.03146525222511453</v>
+        <v>-0.07866469298494949</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.0651099953570683</v>
+        <v>0.1197792828639969</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.05865291137049654</v>
+        <v>0.02448371792547703</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
         <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.002095355033328062</v>
+        <v>0.002101021073924169</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.028375366096534</v>
+        <v>0.06452965016656639</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.006697218875671243</v>
+        <v>-0.03689390876446114</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
@@ -10071,31 +10071,31 @@
         <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.02001850666739925</v>
+        <v>-0.1721570710550577</v>
       </c>
       <c r="GA17" t="n">
         <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.04853288198166399</v>
+        <v>0.1111260012630486</v>
       </c>
       <c r="GC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>-0</v>
